--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="269">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -484,6 +484,84 @@
   </si>
   <si>
     <t>65.</t>
+  </si>
+  <si>
+    <t>RiodeJ</t>
+  </si>
+  <si>
+    <t>66.</t>
+  </si>
+  <si>
+    <t>04.03.26</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро Пан-ди-Асукар</t>
+  </si>
+  <si>
+    <t>67.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро статуя Христа Искупителя</t>
+  </si>
+  <si>
+    <t>68.</t>
+  </si>
+  <si>
+    <t>69.</t>
+  </si>
+  <si>
+    <t>70.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро закат статуя Христа Искупителя</t>
+  </si>
+  <si>
+    <t>71.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро</t>
+  </si>
+  <si>
+    <t>72.</t>
+  </si>
+  <si>
+    <t>73.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро пляж Копакабана</t>
+  </si>
+  <si>
+    <t>74.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вечерний Рио-де-Жанейро </t>
+  </si>
+  <si>
+    <t>75.</t>
+  </si>
+  <si>
+    <t>76.</t>
+  </si>
+  <si>
+    <t>77.</t>
+  </si>
+  <si>
+    <t>Ночной Рио-де-Жанейро</t>
+  </si>
+  <si>
+    <t>78.</t>
+  </si>
+  <si>
+    <t>79.</t>
+  </si>
+  <si>
+    <t>Рассвет Рио-де-Жанейро</t>
+  </si>
+  <si>
+    <t>80.</t>
+  </si>
+  <si>
+    <t>81.</t>
   </si>
   <si>
     <t>Товар</t>
@@ -1748,7 +1826,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
@@ -1821,11 +1899,11 @@
         <v>15</v>
       </c>
       <c r="J2" s="7" t="str">
-        <f t="shared" ref="J2:J51" si="0">C2&amp;D2&amp;E2&amp;F2&amp;G2</f>
+        <f t="shared" ref="J2:J65" si="0">C2&amp;D2&amp;E2&amp;F2&amp;G2</f>
         <v>NtrDeathG01.PQTC.26.02.26</v>
       </c>
       <c r="L2" t="str">
-        <f t="shared" ref="L2:L51" si="1">A2&amp;" "&amp;C2&amp;D2&amp;E2&amp;F2&amp;G2&amp;" "&amp;H2</f>
+        <f t="shared" ref="L2:L65" si="1">A2&amp;" "&amp;C2&amp;D2&amp;E2&amp;F2&amp;G2&amp;" "&amp;H2</f>
         <v>01 NtrDeathG01.PQTC.26.02.26 сериал Игра Смерти</v>
       </c>
     </row>
@@ -3380,11 +3458,11 @@
         <v>130</v>
       </c>
       <c r="J52" s="7" t="str">
-        <f>C52&amp;D52&amp;E52&amp;F52&amp;G52</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket51.PQTC.03.03.26</v>
       </c>
       <c r="L52" t="str">
-        <f>A52&amp;" "&amp;C52&amp;D52&amp;E52&amp;F52&amp;G52&amp;" "&amp;H52</f>
+        <f t="shared" si="1"/>
         <v>51 NtrPhuket51.PQTC.03.03.26 Пхукет Большой Будда</v>
       </c>
     </row>
@@ -3411,11 +3489,11 @@
         <v>130</v>
       </c>
       <c r="J53" s="7" t="str">
-        <f>C53&amp;D53&amp;E53&amp;F53&amp;G53</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket52.PQTC.03.03.26</v>
       </c>
       <c r="L53" t="str">
-        <f>A53&amp;" "&amp;C53&amp;D53&amp;E53&amp;F53&amp;G53&amp;" "&amp;H53</f>
+        <f t="shared" si="1"/>
         <v>52 NtrPhuket52.PQTC.03.03.26 Пхукет Большой Будда</v>
       </c>
     </row>
@@ -3442,11 +3520,11 @@
         <v>133</v>
       </c>
       <c r="J54" s="7" t="str">
-        <f>C54&amp;D54&amp;E54&amp;F54&amp;G54</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket53.PQTC.03.03.26</v>
       </c>
       <c r="L54" t="str">
-        <f>A54&amp;" "&amp;C54&amp;D54&amp;E54&amp;F54&amp;G54&amp;" "&amp;H54</f>
+        <f t="shared" si="1"/>
         <v>53 NtrPhuket53.PQTC.03.03.26 Пхукет Будда Шакьямуни</v>
       </c>
     </row>
@@ -3473,11 +3551,11 @@
         <v>135</v>
       </c>
       <c r="J55" s="7" t="str">
-        <f>C55&amp;D55&amp;E55&amp;F55&amp;G55</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket54.PQTC.03.03.26</v>
       </c>
       <c r="L55" t="str">
-        <f>A55&amp;" "&amp;C55&amp;D55&amp;E55&amp;F55&amp;G55&amp;" "&amp;H55</f>
+        <f t="shared" si="1"/>
         <v>54 NtrPhuket54.PQTC.03.03.26 Пхукет Гуань Инь</v>
       </c>
     </row>
@@ -3504,11 +3582,11 @@
         <v>137</v>
       </c>
       <c r="J56" s="7" t="str">
-        <f>C56&amp;D56&amp;E56&amp;F56&amp;G56</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket55.PQTC.03.03.26</v>
       </c>
       <c r="L56" t="str">
-        <f>A56&amp;" "&amp;C56&amp;D56&amp;E56&amp;F56&amp;G56&amp;" "&amp;H56</f>
+        <f t="shared" si="1"/>
         <v>55 NtrPhuket55.PQTC.03.03.26 Пхукет храм Ват Чалонг</v>
       </c>
     </row>
@@ -3535,11 +3613,11 @@
         <v>137</v>
       </c>
       <c r="J57" s="7" t="str">
-        <f>C57&amp;D57&amp;E57&amp;F57&amp;G57</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket56.PQTC.03.03.26</v>
       </c>
       <c r="L57" t="str">
-        <f>A57&amp;" "&amp;C57&amp;D57&amp;E57&amp;F57&amp;G57&amp;" "&amp;H57</f>
+        <f t="shared" si="1"/>
         <v>56 NtrPhuket56.PQTC.03.03.26 Пхукет храм Ват Чалонг</v>
       </c>
     </row>
@@ -3566,11 +3644,11 @@
         <v>140</v>
       </c>
       <c r="J58" s="7" t="str">
-        <f>C58&amp;D58&amp;E58&amp;F58&amp;G58</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket57.PQTC.03.03.26</v>
       </c>
       <c r="L58" t="str">
-        <f>A58&amp;" "&amp;C58&amp;D58&amp;E58&amp;F58&amp;G58&amp;" "&amp;H58</f>
+        <f t="shared" si="1"/>
         <v>57 NtrPhuket57.PQTC.03.03.26 Пхукет парк FantaSea</v>
       </c>
     </row>
@@ -3597,11 +3675,11 @@
         <v>140</v>
       </c>
       <c r="J59" s="7" t="str">
-        <f>C59&amp;D59&amp;E59&amp;F59&amp;G59</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket58.PQTC.03.03.26</v>
       </c>
       <c r="L59" t="str">
-        <f>A59&amp;" "&amp;C59&amp;D59&amp;E59&amp;F59&amp;G59&amp;" "&amp;H59</f>
+        <f t="shared" si="1"/>
         <v>58 NtrPhuket58.PQTC.03.03.26 Пхукет парк FantaSea</v>
       </c>
     </row>
@@ -3628,11 +3706,11 @@
         <v>143</v>
       </c>
       <c r="J60" s="7" t="str">
-        <f>C60&amp;D60&amp;E60&amp;F60&amp;G60</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket59.PQTC.03.03.26</v>
       </c>
       <c r="L60" t="str">
-        <f>A60&amp;" "&amp;C60&amp;D60&amp;E60&amp;F60&amp;G60&amp;" "&amp;H60</f>
+        <f t="shared" si="1"/>
         <v>59 NtrPhuket59.PQTC.03.03.26 Пхукет закат</v>
       </c>
     </row>
@@ -3659,11 +3737,11 @@
         <v>143</v>
       </c>
       <c r="J61" s="7" t="str">
-        <f>C61&amp;D61&amp;E61&amp;F61&amp;G61</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket60.PQTC.03.03.26</v>
       </c>
       <c r="L61" t="str">
-        <f>A61&amp;" "&amp;C61&amp;D61&amp;E61&amp;F61&amp;G61&amp;" "&amp;H61</f>
+        <f t="shared" si="1"/>
         <v>60 NtrPhuket60.PQTC.03.03.26 Пхукет закат</v>
       </c>
     </row>
@@ -3690,11 +3768,11 @@
         <v>146</v>
       </c>
       <c r="J62" s="7" t="str">
-        <f>C62&amp;D62&amp;E62&amp;F62&amp;G62</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket61.PQTC.03.03.26</v>
       </c>
       <c r="L62" t="str">
-        <f>A62&amp;" "&amp;C62&amp;D62&amp;E62&amp;F62&amp;G62&amp;" "&amp;H62</f>
+        <f t="shared" si="1"/>
         <v>61 NtrPhuket61.PQTC.03.03.26 Пхуке  ночной пляж</v>
       </c>
     </row>
@@ -3721,11 +3799,11 @@
         <v>126</v>
       </c>
       <c r="J63" s="7" t="str">
-        <f>C63&amp;D63&amp;E63&amp;F63&amp;G63</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket62.PQTC.03.03.26</v>
       </c>
       <c r="L63" t="str">
-        <f>A63&amp;" "&amp;C63&amp;D63&amp;E63&amp;F63&amp;G63&amp;" "&amp;H63</f>
+        <f t="shared" si="1"/>
         <v>62 NtrPhuket62.PQTC.03.03.26 Пхукет Пхи Пхи</v>
       </c>
     </row>
@@ -3752,11 +3830,11 @@
         <v>149</v>
       </c>
       <c r="J64" s="7" t="str">
-        <f>C64&amp;D64&amp;E64&amp;F64&amp;G64</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket63.PQTC.03.03.26</v>
       </c>
       <c r="L64" t="str">
-        <f>A64&amp;" "&amp;C64&amp;D64&amp;E64&amp;F64&amp;G64&amp;" "&amp;H64</f>
+        <f t="shared" si="1"/>
         <v>63 NtrPhuket63.PQTC.03.03.26 Пхукет остров Рача-Яй</v>
       </c>
     </row>
@@ -3783,11 +3861,11 @@
         <v>119</v>
       </c>
       <c r="J65" s="7" t="str">
-        <f>C65&amp;D65&amp;E65&amp;F65&amp;G65</f>
+        <f t="shared" si="0"/>
         <v>NtrPhuket64.PQTC.03.03.26</v>
       </c>
       <c r="L65" t="str">
-        <f>A65&amp;" "&amp;C65&amp;D65&amp;E65&amp;F65&amp;G65&amp;" "&amp;H65</f>
+        <f t="shared" si="1"/>
         <v>64 NtrPhuket64.PQTC.03.03.26 Пхукет пейзаж</v>
       </c>
     </row>
@@ -3820,6 +3898,502 @@
       <c r="L66" t="str">
         <f>A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
         <v>65 NtrPhuket65.PQTC.03.03.26 Пхукет пейзаж</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" t="s">
+        <v>153</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H67" t="s">
+        <v>155</v>
+      </c>
+      <c r="J67" s="7" t="str">
+        <f>C67&amp;D67&amp;E67&amp;F67&amp;G67</f>
+        <v>NtrRiodeJ66.PQTC.04.03.26</v>
+      </c>
+      <c r="L67" t="str">
+        <f>A67&amp;" "&amp;C67&amp;D67&amp;E67&amp;F67&amp;G67&amp;" "&amp;H67</f>
+        <v>66 NtrRiodeJ66.PQTC.04.03.26 Рио-де-Жанейро Пан-ди-Асукар</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="5">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H68" t="s">
+        <v>157</v>
+      </c>
+      <c r="J68" s="7" t="str">
+        <f>C68&amp;D68&amp;E68&amp;F68&amp;G68</f>
+        <v>NtrRiodeJ67.PQTC.04.03.26</v>
+      </c>
+      <c r="L68" t="str">
+        <f>A68&amp;" "&amp;C68&amp;D68&amp;E68&amp;F68&amp;G68&amp;" "&amp;H68</f>
+        <v>67 NtrRiodeJ67.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" t="s">
+        <v>158</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H69" t="s">
+        <v>157</v>
+      </c>
+      <c r="J69" s="7" t="str">
+        <f>C69&amp;D69&amp;E69&amp;F69&amp;G69</f>
+        <v>NtrRiodeJ68.PQTC.04.03.26</v>
+      </c>
+      <c r="L69" t="str">
+        <f>A69&amp;" "&amp;C69&amp;D69&amp;E69&amp;F69&amp;G69&amp;" "&amp;H69</f>
+        <v>68 NtrRiodeJ68.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="5">
+        <v>69</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E70" t="s">
+        <v>159</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H70" t="s">
+        <v>157</v>
+      </c>
+      <c r="J70" s="7" t="str">
+        <f>C70&amp;D70&amp;E70&amp;F70&amp;G70</f>
+        <v>NtrRiodeJ69.PQTC.04.03.26</v>
+      </c>
+      <c r="L70" t="str">
+        <f>A70&amp;" "&amp;C70&amp;D70&amp;E70&amp;F70&amp;G70&amp;" "&amp;H70</f>
+        <v>69 NtrRiodeJ69.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
+      <c r="C71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E71" t="s">
+        <v>160</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H71" t="s">
+        <v>161</v>
+      </c>
+      <c r="J71" s="7" t="str">
+        <f>C71&amp;D71&amp;E71&amp;F71&amp;G71</f>
+        <v>NtrRiodeJ70.PQTC.04.03.26</v>
+      </c>
+      <c r="L71" t="str">
+        <f>A71&amp;" "&amp;C71&amp;D71&amp;E71&amp;F71&amp;G71&amp;" "&amp;H71</f>
+        <v>70 NtrRiodeJ70.PQTC.04.03.26 Рио-де-Жанейро закат статуя Христа Искупителя</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E72" t="s">
+        <v>162</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H72" t="s">
+        <v>163</v>
+      </c>
+      <c r="J72" s="7" t="str">
+        <f>C72&amp;D72&amp;E72&amp;F72&amp;G72</f>
+        <v>NtrRiodeJ71.PQTC.04.03.26</v>
+      </c>
+      <c r="L72" t="str">
+        <f>A72&amp;" "&amp;C72&amp;D72&amp;E72&amp;F72&amp;G72&amp;" "&amp;H72</f>
+        <v>71 NtrRiodeJ71.PQTC.04.03.26 Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E73" t="s">
+        <v>164</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H73" t="s">
+        <v>163</v>
+      </c>
+      <c r="J73" s="7" t="str">
+        <f>C73&amp;D73&amp;E73&amp;F73&amp;G73</f>
+        <v>NtrRiodeJ72.PQTC.04.03.26</v>
+      </c>
+      <c r="L73" t="str">
+        <f>A73&amp;" "&amp;C73&amp;D73&amp;E73&amp;F73&amp;G73&amp;" "&amp;H73</f>
+        <v>72 NtrRiodeJ72.PQTC.04.03.26 Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="5">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E74" t="s">
+        <v>165</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H74" t="s">
+        <v>166</v>
+      </c>
+      <c r="J74" s="7" t="str">
+        <f>C74&amp;D74&amp;E74&amp;F74&amp;G74</f>
+        <v>NtrRiodeJ73.PQTC.04.03.26</v>
+      </c>
+      <c r="L74" t="str">
+        <f>A74&amp;" "&amp;C74&amp;D74&amp;E74&amp;F74&amp;G74&amp;" "&amp;H74</f>
+        <v>73 NtrRiodeJ73.PQTC.04.03.26 Рио-де-Жанейро пляж Копакабана</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E75" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H75" t="s">
+        <v>168</v>
+      </c>
+      <c r="J75" s="7" t="str">
+        <f>C75&amp;D75&amp;E75&amp;F75&amp;G75</f>
+        <v>NtrRiodeJ74.PQTC.04.03.26</v>
+      </c>
+      <c r="L75" t="str">
+        <f>A75&amp;" "&amp;C75&amp;D75&amp;E75&amp;F75&amp;G75&amp;" "&amp;H75</f>
+        <v>74 NtrRiodeJ74.PQTC.04.03.26 Вечерний Рио-де-Жанейро </v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E76" t="s">
+        <v>169</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H76" t="s">
+        <v>163</v>
+      </c>
+      <c r="J76" s="7" t="str">
+        <f>C76&amp;D76&amp;E76&amp;F76&amp;G76</f>
+        <v>NtrRiodeJ75.PQTC.04.03.26</v>
+      </c>
+      <c r="L76" t="str">
+        <f>A76&amp;" "&amp;C76&amp;D76&amp;E76&amp;F76&amp;G76&amp;" "&amp;H76</f>
+        <v>75 NtrRiodeJ75.PQTC.04.03.26 Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H77" t="s">
+        <v>163</v>
+      </c>
+      <c r="J77" s="7" t="str">
+        <f>C77&amp;D77&amp;E77&amp;F77&amp;G77</f>
+        <v>NtrRiodeJ76.PQTC.04.03.26</v>
+      </c>
+      <c r="L77" t="str">
+        <f>A77&amp;" "&amp;C77&amp;D77&amp;E77&amp;F77&amp;G77&amp;" "&amp;H77</f>
+        <v>76 NtrRiodeJ76.PQTC.04.03.26 Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E78" t="s">
+        <v>171</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H78" t="s">
+        <v>172</v>
+      </c>
+      <c r="J78" s="7" t="str">
+        <f>C78&amp;D78&amp;E78&amp;F78&amp;G78</f>
+        <v>NtrRiodeJ77.PQTC.04.03.26</v>
+      </c>
+      <c r="L78" t="str">
+        <f>A78&amp;" "&amp;C78&amp;D78&amp;E78&amp;F78&amp;G78&amp;" "&amp;H78</f>
+        <v>77 NtrRiodeJ77.PQTC.04.03.26 Ночной Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
+      <c r="C79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E79" t="s">
+        <v>173</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H79" t="s">
+        <v>172</v>
+      </c>
+      <c r="J79" s="7" t="str">
+        <f>C79&amp;D79&amp;E79&amp;F79&amp;G79</f>
+        <v>NtrRiodeJ78.PQTC.04.03.26</v>
+      </c>
+      <c r="L79" t="str">
+        <f>A79&amp;" "&amp;C79&amp;D79&amp;E79&amp;F79&amp;G79&amp;" "&amp;H79</f>
+        <v>78 NtrRiodeJ78.PQTC.04.03.26 Ночной Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="5">
+        <v>79</v>
+      </c>
+      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E80" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H80" t="s">
+        <v>175</v>
+      </c>
+      <c r="J80" s="7" t="str">
+        <f>C80&amp;D80&amp;E80&amp;F80&amp;G80</f>
+        <v>NtrRiodeJ79.PQTC.04.03.26</v>
+      </c>
+      <c r="L80" t="str">
+        <f>A80&amp;" "&amp;C80&amp;D80&amp;E80&amp;F80&amp;G80&amp;" "&amp;H80</f>
+        <v>79 NtrRiodeJ79.PQTC.04.03.26 Рассвет Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E81" t="s">
+        <v>176</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H81" t="s">
+        <v>175</v>
+      </c>
+      <c r="J81" s="7" t="str">
+        <f>C81&amp;D81&amp;E81&amp;F81&amp;G81</f>
+        <v>NtrRiodeJ80.PQTC.04.03.26</v>
+      </c>
+      <c r="L81" t="str">
+        <f>A81&amp;" "&amp;C81&amp;D81&amp;E81&amp;F81&amp;G81&amp;" "&amp;H81</f>
+        <v>80 NtrRiodeJ80.PQTC.04.03.26 Рассвет Рио-де-Жанейро</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="5">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E82" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H82" t="s">
+        <v>168</v>
+      </c>
+      <c r="J82" s="7" t="str">
+        <f>C82&amp;D82&amp;E82&amp;F82&amp;G82</f>
+        <v>NtrRiodeJ81.PQTC.04.03.26</v>
+      </c>
+      <c r="L82" t="str">
+        <f>A82&amp;" "&amp;C82&amp;D82&amp;E82&amp;F82&amp;G82&amp;" "&amp;H82</f>
+        <v>81 NtrRiodeJ81.PQTC.04.03.26 Вечерний Рио-де-Жанейро </v>
       </c>
     </row>
   </sheetData>
@@ -3848,7 +4422,7 @@
       <formula>LEN($F2)&lt;&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F66">
+  <conditionalFormatting sqref="F18:F82">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEN($F18)&lt;&gt;5</formula>
     </cfRule>
@@ -3877,127 +4451,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" ht="16.35" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -4005,47 +4579,47 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -4053,39 +4627,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -4093,162 +4667,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="289">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -562,6 +562,66 @@
   </si>
   <si>
     <t>81.</t>
+  </si>
+  <si>
+    <t>82.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро собор Святого Себастьяна</t>
+  </si>
+  <si>
+    <t>83.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро Церковь Канделария</t>
+  </si>
+  <si>
+    <t>84.</t>
+  </si>
+  <si>
+    <t>85.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро Муниципальный театр</t>
+  </si>
+  <si>
+    <t>86.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро Музей современного искусства</t>
+  </si>
+  <si>
+    <t>87.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро монумент</t>
+  </si>
+  <si>
+    <t>88.</t>
+  </si>
+  <si>
+    <t>Рио-де-Жанейро Парк Лаге</t>
+  </si>
+  <si>
+    <t>89.</t>
+  </si>
+  <si>
+    <t>Almaty</t>
+  </si>
+  <si>
+    <t>90.</t>
+  </si>
+  <si>
+    <t>Алматы</t>
+  </si>
+  <si>
+    <t>91.</t>
+  </si>
+  <si>
+    <t>Ночные Алматы</t>
+  </si>
+  <si>
+    <t>92.</t>
   </si>
   <si>
     <t>Товар</t>
@@ -1826,7 +1886,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
@@ -3892,11 +3952,11 @@
         <v>119</v>
       </c>
       <c r="J66" s="7" t="str">
-        <f>C66&amp;D66&amp;E66&amp;F66&amp;G66</f>
+        <f t="shared" ref="J66:J82" si="2">C66&amp;D66&amp;E66&amp;F66&amp;G66</f>
         <v>NtrPhuket65.PQTC.03.03.26</v>
       </c>
       <c r="L66" t="str">
-        <f>A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
+        <f t="shared" ref="L66:L82" si="3">A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
         <v>65 NtrPhuket65.PQTC.03.03.26 Пхукет пейзаж</v>
       </c>
     </row>
@@ -3923,11 +3983,11 @@
         <v>155</v>
       </c>
       <c r="J67" s="7" t="str">
-        <f>C67&amp;D67&amp;E67&amp;F67&amp;G67</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ66.PQTC.04.03.26</v>
       </c>
       <c r="L67" t="str">
-        <f>A67&amp;" "&amp;C67&amp;D67&amp;E67&amp;F67&amp;G67&amp;" "&amp;H67</f>
+        <f t="shared" si="3"/>
         <v>66 NtrRiodeJ66.PQTC.04.03.26 Рио-де-Жанейро Пан-ди-Асукар</v>
       </c>
     </row>
@@ -3954,11 +4014,11 @@
         <v>157</v>
       </c>
       <c r="J68" s="7" t="str">
-        <f>C68&amp;D68&amp;E68&amp;F68&amp;G68</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ67.PQTC.04.03.26</v>
       </c>
       <c r="L68" t="str">
-        <f>A68&amp;" "&amp;C68&amp;D68&amp;E68&amp;F68&amp;G68&amp;" "&amp;H68</f>
+        <f t="shared" si="3"/>
         <v>67 NtrRiodeJ67.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</v>
       </c>
     </row>
@@ -3985,11 +4045,11 @@
         <v>157</v>
       </c>
       <c r="J69" s="7" t="str">
-        <f>C69&amp;D69&amp;E69&amp;F69&amp;G69</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ68.PQTC.04.03.26</v>
       </c>
       <c r="L69" t="str">
-        <f>A69&amp;" "&amp;C69&amp;D69&amp;E69&amp;F69&amp;G69&amp;" "&amp;H69</f>
+        <f t="shared" si="3"/>
         <v>68 NtrRiodeJ68.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</v>
       </c>
     </row>
@@ -4016,11 +4076,11 @@
         <v>157</v>
       </c>
       <c r="J70" s="7" t="str">
-        <f>C70&amp;D70&amp;E70&amp;F70&amp;G70</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ69.PQTC.04.03.26</v>
       </c>
       <c r="L70" t="str">
-        <f>A70&amp;" "&amp;C70&amp;D70&amp;E70&amp;F70&amp;G70&amp;" "&amp;H70</f>
+        <f t="shared" si="3"/>
         <v>69 NtrRiodeJ69.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</v>
       </c>
     </row>
@@ -4047,11 +4107,11 @@
         <v>161</v>
       </c>
       <c r="J71" s="7" t="str">
-        <f>C71&amp;D71&amp;E71&amp;F71&amp;G71</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ70.PQTC.04.03.26</v>
       </c>
       <c r="L71" t="str">
-        <f>A71&amp;" "&amp;C71&amp;D71&amp;E71&amp;F71&amp;G71&amp;" "&amp;H71</f>
+        <f t="shared" si="3"/>
         <v>70 NtrRiodeJ70.PQTC.04.03.26 Рио-де-Жанейро закат статуя Христа Искупителя</v>
       </c>
     </row>
@@ -4078,11 +4138,11 @@
         <v>163</v>
       </c>
       <c r="J72" s="7" t="str">
-        <f>C72&amp;D72&amp;E72&amp;F72&amp;G72</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ71.PQTC.04.03.26</v>
       </c>
       <c r="L72" t="str">
-        <f>A72&amp;" "&amp;C72&amp;D72&amp;E72&amp;F72&amp;G72&amp;" "&amp;H72</f>
+        <f t="shared" si="3"/>
         <v>71 NtrRiodeJ71.PQTC.04.03.26 Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4109,11 +4169,11 @@
         <v>163</v>
       </c>
       <c r="J73" s="7" t="str">
-        <f>C73&amp;D73&amp;E73&amp;F73&amp;G73</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ72.PQTC.04.03.26</v>
       </c>
       <c r="L73" t="str">
-        <f>A73&amp;" "&amp;C73&amp;D73&amp;E73&amp;F73&amp;G73&amp;" "&amp;H73</f>
+        <f t="shared" si="3"/>
         <v>72 NtrRiodeJ72.PQTC.04.03.26 Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4140,11 +4200,11 @@
         <v>166</v>
       </c>
       <c r="J74" s="7" t="str">
-        <f>C74&amp;D74&amp;E74&amp;F74&amp;G74</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ73.PQTC.04.03.26</v>
       </c>
       <c r="L74" t="str">
-        <f>A74&amp;" "&amp;C74&amp;D74&amp;E74&amp;F74&amp;G74&amp;" "&amp;H74</f>
+        <f t="shared" si="3"/>
         <v>73 NtrRiodeJ73.PQTC.04.03.26 Рио-де-Жанейро пляж Копакабана</v>
       </c>
     </row>
@@ -4171,11 +4231,11 @@
         <v>168</v>
       </c>
       <c r="J75" s="7" t="str">
-        <f>C75&amp;D75&amp;E75&amp;F75&amp;G75</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ74.PQTC.04.03.26</v>
       </c>
       <c r="L75" t="str">
-        <f>A75&amp;" "&amp;C75&amp;D75&amp;E75&amp;F75&amp;G75&amp;" "&amp;H75</f>
+        <f t="shared" si="3"/>
         <v>74 NtrRiodeJ74.PQTC.04.03.26 Вечерний Рио-де-Жанейро </v>
       </c>
     </row>
@@ -4202,11 +4262,11 @@
         <v>163</v>
       </c>
       <c r="J76" s="7" t="str">
-        <f>C76&amp;D76&amp;E76&amp;F76&amp;G76</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ75.PQTC.04.03.26</v>
       </c>
       <c r="L76" t="str">
-        <f>A76&amp;" "&amp;C76&amp;D76&amp;E76&amp;F76&amp;G76&amp;" "&amp;H76</f>
+        <f t="shared" si="3"/>
         <v>75 NtrRiodeJ75.PQTC.04.03.26 Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4233,11 +4293,11 @@
         <v>163</v>
       </c>
       <c r="J77" s="7" t="str">
-        <f>C77&amp;D77&amp;E77&amp;F77&amp;G77</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ76.PQTC.04.03.26</v>
       </c>
       <c r="L77" t="str">
-        <f>A77&amp;" "&amp;C77&amp;D77&amp;E77&amp;F77&amp;G77&amp;" "&amp;H77</f>
+        <f t="shared" si="3"/>
         <v>76 NtrRiodeJ76.PQTC.04.03.26 Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4264,11 +4324,11 @@
         <v>172</v>
       </c>
       <c r="J78" s="7" t="str">
-        <f>C78&amp;D78&amp;E78&amp;F78&amp;G78</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ77.PQTC.04.03.26</v>
       </c>
       <c r="L78" t="str">
-        <f>A78&amp;" "&amp;C78&amp;D78&amp;E78&amp;F78&amp;G78&amp;" "&amp;H78</f>
+        <f t="shared" si="3"/>
         <v>77 NtrRiodeJ77.PQTC.04.03.26 Ночной Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4295,11 +4355,11 @@
         <v>172</v>
       </c>
       <c r="J79" s="7" t="str">
-        <f>C79&amp;D79&amp;E79&amp;F79&amp;G79</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ78.PQTC.04.03.26</v>
       </c>
       <c r="L79" t="str">
-        <f>A79&amp;" "&amp;C79&amp;D79&amp;E79&amp;F79&amp;G79&amp;" "&amp;H79</f>
+        <f t="shared" si="3"/>
         <v>78 NtrRiodeJ78.PQTC.04.03.26 Ночной Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4326,11 +4386,11 @@
         <v>175</v>
       </c>
       <c r="J80" s="7" t="str">
-        <f>C80&amp;D80&amp;E80&amp;F80&amp;G80</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ79.PQTC.04.03.26</v>
       </c>
       <c r="L80" t="str">
-        <f>A80&amp;" "&amp;C80&amp;D80&amp;E80&amp;F80&amp;G80&amp;" "&amp;H80</f>
+        <f t="shared" si="3"/>
         <v>79 NtrRiodeJ79.PQTC.04.03.26 Рассвет Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4357,11 +4417,11 @@
         <v>175</v>
       </c>
       <c r="J81" s="7" t="str">
-        <f>C81&amp;D81&amp;E81&amp;F81&amp;G81</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ80.PQTC.04.03.26</v>
       </c>
       <c r="L81" t="str">
-        <f>A81&amp;" "&amp;C81&amp;D81&amp;E81&amp;F81&amp;G81&amp;" "&amp;H81</f>
+        <f t="shared" si="3"/>
         <v>80 NtrRiodeJ80.PQTC.04.03.26 Рассвет Рио-де-Жанейро</v>
       </c>
     </row>
@@ -4388,12 +4448,353 @@
         <v>168</v>
       </c>
       <c r="J82" s="7" t="str">
-        <f>C82&amp;D82&amp;E82&amp;F82&amp;G82</f>
+        <f t="shared" si="2"/>
         <v>NtrRiodeJ81.PQTC.04.03.26</v>
       </c>
       <c r="L82" t="str">
-        <f>A82&amp;" "&amp;C82&amp;D82&amp;E82&amp;F82&amp;G82&amp;" "&amp;H82</f>
+        <f t="shared" si="3"/>
         <v>81 NtrRiodeJ81.PQTC.04.03.26 Вечерний Рио-де-Жанейро </v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E83" t="s">
+        <v>178</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J83" s="7" t="str">
+        <f>C83&amp;D83&amp;E83&amp;F83&amp;G83</f>
+        <v>NtrRiodeJ82.PQTC.04.03.26</v>
+      </c>
+      <c r="L83" t="str">
+        <f>A83&amp;" "&amp;C83&amp;D83&amp;E83&amp;F83&amp;G83&amp;" "&amp;H83</f>
+        <v>82 NtrRiodeJ82.PQTC.04.03.26 Рио-де-Жанейро собор Святого Себастьяна</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E84" t="s">
+        <v>180</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="J84" s="7" t="str">
+        <f>C84&amp;D84&amp;E84&amp;F84&amp;G84</f>
+        <v>NtrRiodeJ83.PQTC.04.03.26</v>
+      </c>
+      <c r="L84" t="str">
+        <f>A84&amp;" "&amp;C84&amp;D84&amp;E84&amp;F84&amp;G84&amp;" "&amp;H84</f>
+        <v>83 NtrRiodeJ83.PQTC.04.03.26 Рио-де-Жанейро Церковь Канделария</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E85" t="s">
+        <v>182</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="J85" s="7" t="str">
+        <f>C85&amp;D85&amp;E85&amp;F85&amp;G85</f>
+        <v>NtrRiodeJ84.PQTC.04.03.26</v>
+      </c>
+      <c r="L85" t="str">
+        <f>A85&amp;" "&amp;C85&amp;D85&amp;E85&amp;F85&amp;G85&amp;" "&amp;H85</f>
+        <v>84 NtrRiodeJ84.PQTC.04.03.26 Рио-де-Жанейро Церковь Канделария</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E86" t="s">
+        <v>183</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="J86" s="7" t="str">
+        <f>C86&amp;D86&amp;E86&amp;F86&amp;G86</f>
+        <v>NtrRiodeJ85.PQTC.04.03.26</v>
+      </c>
+      <c r="L86" t="str">
+        <f>A86&amp;" "&amp;C86&amp;D86&amp;E86&amp;F86&amp;G86&amp;" "&amp;H86</f>
+        <v>85 NtrRiodeJ85.PQTC.04.03.26 Рио-де-Жанейро Муниципальный театр</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="C87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E87" t="s">
+        <v>185</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="J87" s="7" t="str">
+        <f>C87&amp;D87&amp;E87&amp;F87&amp;G87</f>
+        <v>NtrRiodeJ86.PQTC.04.03.26</v>
+      </c>
+      <c r="L87" t="str">
+        <f>A87&amp;" "&amp;C87&amp;D87&amp;E87&amp;F87&amp;G87&amp;" "&amp;H87</f>
+        <v>86 NtrRiodeJ86.PQTC.04.03.26 Рио-де-Жанейро Музей современного искусства</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E88" t="s">
+        <v>187</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H88" t="s">
+        <v>188</v>
+      </c>
+      <c r="J88" s="7" t="str">
+        <f>C88&amp;D88&amp;E88&amp;F88&amp;G88</f>
+        <v>NtrRiodeJ87.PQTC.04.03.26</v>
+      </c>
+      <c r="L88" t="str">
+        <f>A88&amp;" "&amp;C88&amp;D88&amp;E88&amp;F88&amp;G88&amp;" "&amp;H88</f>
+        <v>87 NtrRiodeJ87.PQTC.04.03.26 Рио-де-Жанейро монумент</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" t="s">
+        <v>189</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H89" t="s">
+        <v>190</v>
+      </c>
+      <c r="J89" s="7" t="str">
+        <f>C89&amp;D89&amp;E89&amp;F89&amp;G89</f>
+        <v>NtrRiodeJ88.PQTC.04.03.26</v>
+      </c>
+      <c r="L89" t="str">
+        <f>A89&amp;" "&amp;C89&amp;D89&amp;E89&amp;F89&amp;G89&amp;" "&amp;H89</f>
+        <v>88 NtrRiodeJ88.PQTC.04.03.26 Рио-де-Жанейро Парк Лаге</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E90" t="s">
+        <v>191</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H90" t="s">
+        <v>190</v>
+      </c>
+      <c r="J90" s="7" t="str">
+        <f>C90&amp;D90&amp;E90&amp;F90&amp;G90</f>
+        <v>NtrRiodeJ89.PQTC.04.03.26</v>
+      </c>
+      <c r="L90" t="str">
+        <f>A90&amp;" "&amp;C90&amp;D90&amp;E90&amp;F90&amp;G90&amp;" "&amp;H90</f>
+        <v>89 NtrRiodeJ89.PQTC.04.03.26 Рио-де-Жанейро Парк Лаге</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E91" t="s">
+        <v>193</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H91" t="s">
+        <v>194</v>
+      </c>
+      <c r="J91" s="7" t="str">
+        <f>C91&amp;D91&amp;E91&amp;F91&amp;G91</f>
+        <v>NtrAlmaty90.PQTC.04.03.26</v>
+      </c>
+      <c r="L91" t="str">
+        <f>A91&amp;" "&amp;C91&amp;D91&amp;E91&amp;F91&amp;G91&amp;" "&amp;H91</f>
+        <v>90 NtrAlmaty90.PQTC.04.03.26 Алматы</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
+      <c r="C92" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" t="s">
+        <v>195</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H92" t="s">
+        <v>196</v>
+      </c>
+      <c r="J92" s="7" t="str">
+        <f>C92&amp;D92&amp;E92&amp;F92&amp;G92</f>
+        <v>NtrAlmaty91.PQTC.04.03.26</v>
+      </c>
+      <c r="L92" t="str">
+        <f>A92&amp;" "&amp;C92&amp;D92&amp;E92&amp;F92&amp;G92&amp;" "&amp;H92</f>
+        <v>91 NtrAlmaty91.PQTC.04.03.26 Ночные Алматы</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E93" t="s">
+        <v>197</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H93" t="s">
+        <v>196</v>
+      </c>
+      <c r="J93" s="7" t="str">
+        <f>C93&amp;D93&amp;E93&amp;F93&amp;G93</f>
+        <v>NtrAlmaty92.PQTC.04.03.26</v>
+      </c>
+      <c r="L93" t="str">
+        <f>A93&amp;" "&amp;C93&amp;D93&amp;E93&amp;F93&amp;G93&amp;" "&amp;H93</f>
+        <v>92 NtrAlmaty92.PQTC.04.03.26 Ночные Алматы</v>
       </c>
     </row>
   </sheetData>
@@ -4422,7 +4823,7 @@
       <formula>LEN($F2)&lt;&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F82">
+  <conditionalFormatting sqref="F18:F93">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEN($F18)&lt;&gt;5</formula>
     </cfRule>
@@ -4451,127 +4852,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="16.35" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -4579,47 +4980,47 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -4627,39 +5028,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -4667,162 +5068,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="294">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -567,6 +567,9 @@
     <t>82.</t>
   </si>
   <si>
+    <t>05.03.26</t>
+  </si>
+  <si>
     <t>Рио-де-Жанейро собор Святого Себастьяна</t>
   </si>
   <si>
@@ -624,6 +627,21 @@
     <t>92.</t>
   </si>
   <si>
+    <t>Ops</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>06.03.26</t>
+  </si>
+  <si>
+    <t>Планеты</t>
+  </si>
+  <si>
     <t>Товар</t>
   </si>
   <si>
@@ -730,9 +748,6 @@
   </si>
   <si>
     <t>Обложка на паспорта экокожа</t>
-  </si>
-  <si>
-    <t>Ops</t>
   </si>
   <si>
     <t>Обложка на студенческий экокожа</t>
@@ -1886,7 +1901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
@@ -3952,11 +3967,11 @@
         <v>119</v>
       </c>
       <c r="J66" s="7" t="str">
-        <f t="shared" ref="J66:J82" si="2">C66&amp;D66&amp;E66&amp;F66&amp;G66</f>
+        <f t="shared" ref="J66:J93" si="2">C66&amp;D66&amp;E66&amp;F66&amp;G66</f>
         <v>NtrPhuket65.PQTC.03.03.26</v>
       </c>
       <c r="L66" t="str">
-        <f t="shared" ref="L66:L82" si="3">A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
+        <f t="shared" ref="L66:L93" si="3">A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
         <v>65 NtrPhuket65.PQTC.03.03.26 Пхукет пейзаж</v>
       </c>
     </row>
@@ -4473,18 +4488,18 @@
         <v>13</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J83" s="7" t="str">
-        <f>C83&amp;D83&amp;E83&amp;F83&amp;G83</f>
-        <v>NtrRiodeJ82.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ82.PQTC.05.03.26</v>
       </c>
       <c r="L83" t="str">
-        <f>A83&amp;" "&amp;C83&amp;D83&amp;E83&amp;F83&amp;G83&amp;" "&amp;H83</f>
-        <v>82 NtrRiodeJ82.PQTC.04.03.26 Рио-де-Жанейро собор Святого Себастьяна</v>
+        <f t="shared" si="3"/>
+        <v>82 NtrRiodeJ82.PQTC.05.03.26 Рио-де-Жанейро собор Святого Себастьяна</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4498,24 +4513,24 @@
         <v>152</v>
       </c>
       <c r="E84" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J84" s="7" t="str">
-        <f>C84&amp;D84&amp;E84&amp;F84&amp;G84</f>
-        <v>NtrRiodeJ83.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ83.PQTC.05.03.26</v>
       </c>
       <c r="L84" t="str">
-        <f>A84&amp;" "&amp;C84&amp;D84&amp;E84&amp;F84&amp;G84&amp;" "&amp;H84</f>
-        <v>83 NtrRiodeJ83.PQTC.04.03.26 Рио-де-Жанейро Церковь Канделария</v>
+        <f t="shared" si="3"/>
+        <v>83 NtrRiodeJ83.PQTC.05.03.26 Рио-де-Жанейро Церковь Канделария</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4529,24 +4544,24 @@
         <v>152</v>
       </c>
       <c r="E85" t="s">
+        <v>183</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H85" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H85" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="J85" s="7" t="str">
-        <f>C85&amp;D85&amp;E85&amp;F85&amp;G85</f>
-        <v>NtrRiodeJ84.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ84.PQTC.05.03.26</v>
       </c>
       <c r="L85" t="str">
-        <f>A85&amp;" "&amp;C85&amp;D85&amp;E85&amp;F85&amp;G85&amp;" "&amp;H85</f>
-        <v>84 NtrRiodeJ84.PQTC.04.03.26 Рио-де-Жанейро Церковь Канделария</v>
+        <f t="shared" si="3"/>
+        <v>84 NtrRiodeJ84.PQTC.05.03.26 Рио-де-Жанейро Церковь Канделария</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4560,24 +4575,24 @@
         <v>152</v>
       </c>
       <c r="E86" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J86" s="7" t="str">
-        <f>C86&amp;D86&amp;E86&amp;F86&amp;G86</f>
-        <v>NtrRiodeJ85.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ85.PQTC.05.03.26</v>
       </c>
       <c r="L86" t="str">
-        <f>A86&amp;" "&amp;C86&amp;D86&amp;E86&amp;F86&amp;G86&amp;" "&amp;H86</f>
-        <v>85 NtrRiodeJ85.PQTC.04.03.26 Рио-де-Жанейро Муниципальный театр</v>
+        <f t="shared" si="3"/>
+        <v>85 NtrRiodeJ85.PQTC.05.03.26 Рио-де-Жанейро Муниципальный театр</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4591,24 +4606,24 @@
         <v>152</v>
       </c>
       <c r="E87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J87" s="7" t="str">
-        <f>C87&amp;D87&amp;E87&amp;F87&amp;G87</f>
-        <v>NtrRiodeJ86.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ86.PQTC.05.03.26</v>
       </c>
       <c r="L87" t="str">
-        <f>A87&amp;" "&amp;C87&amp;D87&amp;E87&amp;F87&amp;G87&amp;" "&amp;H87</f>
-        <v>86 NtrRiodeJ86.PQTC.04.03.26 Рио-де-Жанейро Музей современного искусства</v>
+        <f t="shared" si="3"/>
+        <v>86 NtrRiodeJ86.PQTC.05.03.26 Рио-де-Жанейро Музей современного искусства</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4622,24 +4637,24 @@
         <v>152</v>
       </c>
       <c r="E88" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J88" s="7" t="str">
-        <f>C88&amp;D88&amp;E88&amp;F88&amp;G88</f>
-        <v>NtrRiodeJ87.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ87.PQTC.05.03.26</v>
       </c>
       <c r="L88" t="str">
-        <f>A88&amp;" "&amp;C88&amp;D88&amp;E88&amp;F88&amp;G88&amp;" "&amp;H88</f>
-        <v>87 NtrRiodeJ87.PQTC.04.03.26 Рио-де-Жанейро монумент</v>
+        <f t="shared" si="3"/>
+        <v>87 NtrRiodeJ87.PQTC.05.03.26 Рио-де-Жанейро монумент</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4653,24 +4668,24 @@
         <v>152</v>
       </c>
       <c r="E89" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J89" s="7" t="str">
-        <f>C89&amp;D89&amp;E89&amp;F89&amp;G89</f>
-        <v>NtrRiodeJ88.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ88.PQTC.05.03.26</v>
       </c>
       <c r="L89" t="str">
-        <f>A89&amp;" "&amp;C89&amp;D89&amp;E89&amp;F89&amp;G89&amp;" "&amp;H89</f>
-        <v>88 NtrRiodeJ88.PQTC.04.03.26 Рио-де-Жанейро Парк Лаге</v>
+        <f t="shared" si="3"/>
+        <v>88 NtrRiodeJ88.PQTC.05.03.26 Рио-де-Жанейро Парк Лаге</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4684,24 +4699,24 @@
         <v>152</v>
       </c>
       <c r="E90" t="s">
+        <v>192</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H90" t="s">
         <v>191</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H90" t="s">
-        <v>190</v>
-      </c>
       <c r="J90" s="7" t="str">
-        <f>C90&amp;D90&amp;E90&amp;F90&amp;G90</f>
-        <v>NtrRiodeJ89.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrRiodeJ89.PQTC.05.03.26</v>
       </c>
       <c r="L90" t="str">
-        <f>A90&amp;" "&amp;C90&amp;D90&amp;E90&amp;F90&amp;G90&amp;" "&amp;H90</f>
-        <v>89 NtrRiodeJ89.PQTC.04.03.26 Рио-де-Жанейро Парк Лаге</v>
+        <f t="shared" si="3"/>
+        <v>89 NtrRiodeJ89.PQTC.05.03.26 Рио-де-Жанейро Парк Лаге</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4712,27 +4727,27 @@
         <v>10</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E91" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H91" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J91" s="7" t="str">
-        <f>C91&amp;D91&amp;E91&amp;F91&amp;G91</f>
-        <v>NtrAlmaty90.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty90.PQTC.05.03.26</v>
       </c>
       <c r="L91" t="str">
-        <f>A91&amp;" "&amp;C91&amp;D91&amp;E91&amp;F91&amp;G91&amp;" "&amp;H91</f>
-        <v>90 NtrAlmaty90.PQTC.04.03.26 Алматы</v>
+        <f t="shared" si="3"/>
+        <v>90 NtrAlmaty90.PQTC.05.03.26 Алматы</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4743,27 +4758,27 @@
         <v>10</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E92" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="H92" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J92" s="7" t="str">
-        <f>C92&amp;D92&amp;E92&amp;F92&amp;G92</f>
-        <v>NtrAlmaty91.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty91.PQTC.05.03.26</v>
       </c>
       <c r="L92" t="str">
-        <f>A92&amp;" "&amp;C92&amp;D92&amp;E92&amp;F92&amp;G92&amp;" "&amp;H92</f>
-        <v>91 NtrAlmaty91.PQTC.04.03.26 Ночные Алматы</v>
+        <f t="shared" si="3"/>
+        <v>91 NtrAlmaty91.PQTC.05.03.26 Ночные Алматы</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4774,27 +4789,55 @@
         <v>10</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E93" t="s">
+        <v>198</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H93" t="s">
         <v>197</v>
       </c>
-      <c r="F93" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H93" t="s">
-        <v>196</v>
-      </c>
       <c r="J93" s="7" t="str">
-        <f>C93&amp;D93&amp;E93&amp;F93&amp;G93</f>
-        <v>NtrAlmaty92.PQTC.04.03.26</v>
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty92.PQTC.05.03.26</v>
       </c>
       <c r="L93" t="str">
-        <f>A93&amp;" "&amp;C93&amp;D93&amp;E93&amp;F93&amp;G93&amp;" "&amp;H93</f>
-        <v>92 NtrAlmaty92.PQTC.04.03.26 Ночные Алматы</v>
+        <f t="shared" si="3"/>
+        <v>92 NtrAlmaty92.PQTC.05.03.26 Ночные Алматы</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12">
+      <c r="C94" t="s">
+        <v>199</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E94" t="s">
+        <v>201</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="H94" t="s">
+        <v>203</v>
+      </c>
+      <c r="J94" s="7" t="str">
+        <f>C94&amp;D94&amp;E94&amp;F94&amp;G94</f>
+        <v>OpsPlanet.PQTC.06.03.26</v>
+      </c>
+      <c r="L94" t="str">
+        <f>A94&amp;" "&amp;C94&amp;D94&amp;E94&amp;F94&amp;G94&amp;" "&amp;H94</f>
+        <v> OpsPlanet.PQTC.06.03.26 Планеты</v>
       </c>
     </row>
   </sheetData>
@@ -4823,7 +4866,7 @@
       <formula>LEN($F2)&lt;&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F93">
+  <conditionalFormatting sqref="F18:F94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEN($F18)&lt;&gt;5</formula>
     </cfRule>
@@ -4852,127 +4895,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" ht="16.35" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -4980,47 +5023,47 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -5028,39 +5071,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -5068,162 +5111,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9150"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Артикулы" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="320">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -627,19 +627,97 @@
     <t>92.</t>
   </si>
   <si>
+    <t>93.</t>
+  </si>
+  <si>
+    <t>07.03.26</t>
+  </si>
+  <si>
+    <t>94.</t>
+  </si>
+  <si>
+    <t>Вечерний Алматы</t>
+  </si>
+  <si>
+    <t>95.</t>
+  </si>
+  <si>
+    <t>Алматы беседка Ротонда</t>
+  </si>
+  <si>
+    <t>96.</t>
+  </si>
+  <si>
+    <t>97.</t>
+  </si>
+  <si>
+    <t>Алматы парк Кок-Тобе</t>
+  </si>
+  <si>
+    <t>98.</t>
+  </si>
+  <si>
+    <t>99.</t>
+  </si>
+  <si>
+    <t>Алматы Вознесенский собор</t>
+  </si>
+  <si>
+    <t>100.</t>
+  </si>
+  <si>
+    <t>101.</t>
+  </si>
+  <si>
+    <t>Алматы Свято-Никольский собор</t>
+  </si>
+  <si>
+    <t>102.</t>
+  </si>
+  <si>
+    <t>Алматы Центральная мечеть</t>
+  </si>
+  <si>
+    <t>103.</t>
+  </si>
+  <si>
+    <t>104.</t>
+  </si>
+  <si>
+    <t>105.</t>
+  </si>
+  <si>
+    <t>106.</t>
+  </si>
+  <si>
+    <t>Алматы Центральная площадь</t>
+  </si>
+  <si>
+    <t>107.</t>
+  </si>
+  <si>
+    <t>Алматы здание Верховного совета</t>
+  </si>
+  <si>
+    <t>108.</t>
+  </si>
+  <si>
+    <t>Алматы Бакшасарай</t>
+  </si>
+  <si>
     <t>Ops</t>
   </si>
   <si>
     <t>Planet</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>06.03.26</t>
+    <t>124.</t>
   </si>
   <si>
     <t>Планеты</t>
+  </si>
+  <si>
+    <t>125.</t>
   </si>
   <si>
     <t>Товар</t>
@@ -1901,21 +1979,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
     <col min="2" max="2" width="3.66666666666667" customWidth="1"/>
     <col min="3" max="3" width="15.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.4385964912281" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15.5526315789474" customWidth="1"/>
+    <col min="4" max="4" width="11.4351851851852" style="6" customWidth="1"/>
+    <col min="5" max="5" width="15.5555555555556" customWidth="1"/>
     <col min="6" max="6" width="11.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="9.8859649122807" style="7" customWidth="1"/>
-    <col min="8" max="8" width="28.1052631578947" customWidth="1"/>
-    <col min="9" max="9" width="7.55263157894737" customWidth="1"/>
+    <col min="7" max="7" width="9.88888888888889" style="7" customWidth="1"/>
+    <col min="8" max="8" width="28.1018518518519" customWidth="1"/>
+    <col min="9" max="9" width="7.55555555555556" customWidth="1"/>
     <col min="10" max="10" width="29.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="66.8859649122807" customWidth="1"/>
-    <col min="16" max="16" width="8.8859649122807" customWidth="1"/>
+    <col min="12" max="12" width="66.8888888888889" customWidth="1"/>
+    <col min="16" max="16" width="8.88888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="39" customHeight="1" spans="1:12">
@@ -3967,11 +4045,11 @@
         <v>119</v>
       </c>
       <c r="J66" s="7" t="str">
-        <f t="shared" ref="J66:J93" si="2">C66&amp;D66&amp;E66&amp;F66&amp;G66</f>
+        <f t="shared" ref="J66:J97" si="2">C66&amp;D66&amp;E66&amp;F66&amp;G66</f>
         <v>NtrPhuket65.PQTC.03.03.26</v>
       </c>
       <c r="L66" t="str">
-        <f t="shared" ref="L66:L93" si="3">A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
+        <f t="shared" ref="L66:L97" si="3">A66&amp;" "&amp;C66&amp;D66&amp;E66&amp;F66&amp;G66&amp;" "&amp;H66</f>
         <v>65 NtrPhuket65.PQTC.03.03.26 Пхукет пейзаж</v>
       </c>
     </row>
@@ -4812,32 +4890,562 @@
         <v>92 NtrAlmaty92.PQTC.05.03.26 Ночные Алматы</v>
       </c>
     </row>
-    <row r="94" spans="3:12">
+    <row r="94" spans="1:12">
+      <c r="A94" s="5">
+        <v>93</v>
+      </c>
       <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E94" t="s">
         <v>199</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="F94" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E94" t="s">
+      <c r="H94" t="s">
+        <v>197</v>
+      </c>
+      <c r="J94" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty93.PQTC.07.03.26</v>
+      </c>
+      <c r="L94" t="str">
+        <f t="shared" si="3"/>
+        <v>93 NtrAlmaty93.PQTC.07.03.26 Ночные Алматы</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E95" t="s">
         <v>201</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="7" t="s">
+      <c r="F95" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H95" t="s">
         <v>202</v>
       </c>
-      <c r="H94" t="s">
+      <c r="J95" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty94.PQTC.07.03.26</v>
+      </c>
+      <c r="L95" t="str">
+        <f t="shared" si="3"/>
+        <v>94 NtrAlmaty94.PQTC.07.03.26 Вечерний Алматы</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" s="5">
+        <v>95</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E96" t="s">
         <v>203</v>
       </c>
-      <c r="J94" s="7" t="str">
-        <f>C94&amp;D94&amp;E94&amp;F94&amp;G94</f>
-        <v>OpsPlanet.PQTC.06.03.26</v>
-      </c>
-      <c r="L94" t="str">
-        <f>A94&amp;" "&amp;C94&amp;D94&amp;E94&amp;F94&amp;G94&amp;" "&amp;H94</f>
-        <v> OpsPlanet.PQTC.06.03.26 Планеты</v>
+      <c r="F96" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H96" t="s">
+        <v>204</v>
+      </c>
+      <c r="J96" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty95.PQTC.07.03.26</v>
+      </c>
+      <c r="L96" t="str">
+        <f t="shared" si="3"/>
+        <v>95 NtrAlmaty95.PQTC.07.03.26 Алматы беседка Ротонда</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E97" t="s">
+        <v>205</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H97" t="s">
+        <v>204</v>
+      </c>
+      <c r="J97" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>NtrAlmaty96.PQTC.07.03.26</v>
+      </c>
+      <c r="L97" t="str">
+        <f t="shared" si="3"/>
+        <v>96 NtrAlmaty96.PQTC.07.03.26 Алматы беседка Ротонда</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="5">
+        <v>97</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E98" t="s">
+        <v>206</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H98" t="s">
+        <v>207</v>
+      </c>
+      <c r="J98" s="7" t="str">
+        <f>C98&amp;D98&amp;E98&amp;F98&amp;G98</f>
+        <v>NtrAlmaty97.PQTC.07.03.26</v>
+      </c>
+      <c r="L98" t="str">
+        <f>A98&amp;" "&amp;C98&amp;D98&amp;E98&amp;F98&amp;G98&amp;" "&amp;H98</f>
+        <v>97 NtrAlmaty97.PQTC.07.03.26 Алматы парк Кок-Тобе</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E99" t="s">
+        <v>208</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H99" t="s">
+        <v>207</v>
+      </c>
+      <c r="J99" s="7" t="str">
+        <f>C99&amp;D99&amp;E99&amp;F99&amp;G99</f>
+        <v>NtrAlmaty98.PQTC.07.03.26</v>
+      </c>
+      <c r="L99" t="str">
+        <f>A99&amp;" "&amp;C99&amp;D99&amp;E99&amp;F99&amp;G99&amp;" "&amp;H99</f>
+        <v>98 NtrAlmaty98.PQTC.07.03.26 Алматы парк Кок-Тобе</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="5">
+        <v>99</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" t="s">
+        <v>209</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H100" t="s">
+        <v>210</v>
+      </c>
+      <c r="J100" s="7" t="str">
+        <f>C100&amp;D100&amp;E100&amp;F100&amp;G100</f>
+        <v>NtrAlmaty99.PQTC.07.03.26</v>
+      </c>
+      <c r="L100" t="str">
+        <f>A100&amp;" "&amp;C100&amp;D100&amp;E100&amp;F100&amp;G100&amp;" "&amp;H100</f>
+        <v>99 NtrAlmaty99.PQTC.07.03.26 Алматы Вознесенский собор</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E101" t="s">
+        <v>211</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H101" t="s">
+        <v>210</v>
+      </c>
+      <c r="J101" s="7" t="str">
+        <f>C101&amp;D101&amp;E101&amp;F101&amp;G101</f>
+        <v>NtrAlmaty100.PQTC.07.03.26</v>
+      </c>
+      <c r="L101" t="str">
+        <f>A101&amp;" "&amp;C101&amp;D101&amp;E101&amp;F101&amp;G101&amp;" "&amp;H101</f>
+        <v>100 NtrAlmaty100.PQTC.07.03.26 Алматы Вознесенский собор</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="5">
+        <v>101</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E102" t="s">
+        <v>212</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H102" t="s">
+        <v>213</v>
+      </c>
+      <c r="J102" s="7" t="str">
+        <f>C102&amp;D102&amp;E102&amp;F102&amp;G102</f>
+        <v>NtrAlmaty101.PQTC.07.03.26</v>
+      </c>
+      <c r="L102" t="str">
+        <f>A102&amp;" "&amp;C102&amp;D102&amp;E102&amp;F102&amp;G102&amp;" "&amp;H102</f>
+        <v>101 NtrAlmaty101.PQTC.07.03.26 Алматы Свято-Никольский собор</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="5">
+        <v>102</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E103" t="s">
+        <v>214</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H103" t="s">
+        <v>215</v>
+      </c>
+      <c r="J103" s="7" t="str">
+        <f>C103&amp;D103&amp;E103&amp;F103&amp;G103</f>
+        <v>NtrAlmaty102.PQTC.07.03.26</v>
+      </c>
+      <c r="L103" t="str">
+        <f>A103&amp;" "&amp;C103&amp;D103&amp;E103&amp;F103&amp;G103&amp;" "&amp;H103</f>
+        <v>102 NtrAlmaty102.PQTC.07.03.26 Алматы Центральная мечеть</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" s="5">
+        <v>103</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E104" t="s">
+        <v>216</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H104" t="s">
+        <v>215</v>
+      </c>
+      <c r="J104" s="7" t="str">
+        <f>C104&amp;D104&amp;E104&amp;F104&amp;G104</f>
+        <v>NtrAlmaty103.PQTC.07.03.26</v>
+      </c>
+      <c r="L104" t="str">
+        <f>A104&amp;" "&amp;C104&amp;D104&amp;E104&amp;F104&amp;G104&amp;" "&amp;H104</f>
+        <v>103 NtrAlmaty103.PQTC.07.03.26 Алматы Центральная мечеть</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" s="5">
+        <v>104</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E105" t="s">
+        <v>217</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H105" t="s">
+        <v>195</v>
+      </c>
+      <c r="J105" s="7" t="str">
+        <f>C105&amp;D105&amp;E105&amp;F105&amp;G105</f>
+        <v>NtrAlmaty104.PQTC.07.03.26</v>
+      </c>
+      <c r="L105" t="str">
+        <f>A105&amp;" "&amp;C105&amp;D105&amp;E105&amp;F105&amp;G105&amp;" "&amp;H105</f>
+        <v>104 NtrAlmaty104.PQTC.07.03.26 Алматы</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" s="5">
+        <v>105</v>
+      </c>
+      <c r="C106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E106" t="s">
+        <v>218</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H106" t="s">
+        <v>215</v>
+      </c>
+      <c r="J106" s="7" t="str">
+        <f>C106&amp;D106&amp;E106&amp;F106&amp;G106</f>
+        <v>NtrAlmaty105.PQTC.07.03.26</v>
+      </c>
+      <c r="L106" t="str">
+        <f>A106&amp;" "&amp;C106&amp;D106&amp;E106&amp;F106&amp;G106&amp;" "&amp;H106</f>
+        <v>105 NtrAlmaty105.PQTC.07.03.26 Алматы Центральная мечеть</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" s="5">
+        <v>106</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E107" t="s">
+        <v>219</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H107" t="s">
+        <v>220</v>
+      </c>
+      <c r="J107" s="7" t="str">
+        <f>C107&amp;D107&amp;E107&amp;F107&amp;G107</f>
+        <v>NtrAlmaty106.PQTC.07.03.26</v>
+      </c>
+      <c r="L107" t="str">
+        <f>A107&amp;" "&amp;C107&amp;D107&amp;E107&amp;F107&amp;G107&amp;" "&amp;H107</f>
+        <v>106 NtrAlmaty106.PQTC.07.03.26 Алматы Центральная площадь</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" s="5">
+        <v>107</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E108" t="s">
+        <v>221</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H108" t="s">
+        <v>222</v>
+      </c>
+      <c r="J108" s="7" t="str">
+        <f>C108&amp;D108&amp;E108&amp;F108&amp;G108</f>
+        <v>NtrAlmaty107.PQTC.07.03.26</v>
+      </c>
+      <c r="L108" t="str">
+        <f>A108&amp;" "&amp;C108&amp;D108&amp;E108&amp;F108&amp;G108&amp;" "&amp;H108</f>
+        <v>107 NtrAlmaty107.PQTC.07.03.26 Алматы здание Верховного совета</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" s="5">
+        <v>108</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E109" t="s">
+        <v>223</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H109" t="s">
+        <v>224</v>
+      </c>
+      <c r="J109" s="7" t="str">
+        <f>C109&amp;D109&amp;E109&amp;F109&amp;G109</f>
+        <v>NtrAlmaty108.PQTC.07.03.26</v>
+      </c>
+      <c r="L109" t="str">
+        <f>A109&amp;" "&amp;C109&amp;D109&amp;E109&amp;F109&amp;G109&amp;" "&amp;H109</f>
+        <v>108 NtrAlmaty108.PQTC.07.03.26 Алматы Бакшасарай</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" s="5">
+        <v>124</v>
+      </c>
+      <c r="C125" t="s">
+        <v>225</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E125" t="s">
+        <v>227</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H125" t="s">
+        <v>228</v>
+      </c>
+      <c r="J125" s="7" t="str">
+        <f>C125&amp;D125&amp;E125&amp;F125&amp;G125</f>
+        <v>OpsPlanet124.PQTC.07.03.26</v>
+      </c>
+      <c r="L125" t="str">
+        <f>A125&amp;" "&amp;C125&amp;D125&amp;E125&amp;F125&amp;G125&amp;" "&amp;H125</f>
+        <v>124 OpsPlanet124.PQTC.07.03.26 Планеты</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" s="5">
+        <v>125</v>
+      </c>
+      <c r="C126" t="s">
+        <v>225</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E126" t="s">
+        <v>229</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H126" t="s">
+        <v>228</v>
+      </c>
+      <c r="J126" s="7" t="str">
+        <f>C126&amp;D126&amp;E126&amp;F126&amp;G126</f>
+        <v>OpsPlanet125.PQTC.07.03.26</v>
+      </c>
+      <c r="L126" t="str">
+        <f>A126&amp;" "&amp;C126&amp;D126&amp;E126&amp;F126&amp;G126&amp;" "&amp;H126</f>
+        <v>125 OpsPlanet125.PQTC.07.03.26 Планеты</v>
       </c>
     </row>
   </sheetData>
@@ -4866,14 +5474,14 @@
       <formula>LEN($F2)&lt;&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F94">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>LEN($F18)&lt;&gt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>LEN($G2)&lt;&gt;8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18:F109;F125:F126">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>LEN($F18)&lt;&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4886,136 +5494,136 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="9.10526315789474" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9.10185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="45.1052631578947" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.8859649122807" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.10526315789474" style="1"/>
+    <col min="1" max="1" width="45.1018518518519" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.10185185185185" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" ht="16.35" spans="1:2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -5023,47 +5631,47 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -5071,39 +5679,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -5111,162 +5719,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
